--- a/cg/apps/invoice/templates/KI_sample_invoice.xlsx
+++ b/cg/apps/invoice/templates/KI_sample_invoice.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10107"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10404"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christian/Documents/clinicalGenomics/cg/cg/apps/invoice/templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linnealofdahl/dev/cg/cg/apps/invoice/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50D334E-FA9F-7948-AB5F-229B438DB16A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7EDB69-440E-6843-A927-C4E3ACCB3B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="15100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -105,13 +105,13 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Anna Zetterlund</t>
+    <t>Anna Gellerbring</t>
   </si>
   <si>
-    <t>anna.zetterlund@scilifelab.se</t>
+    <t>anna.gellerbring@scilifelab.se</t>
   </si>
   <si>
-    <t>(+46) 701523463</t>
+    <t>(+46) 701904409</t>
   </si>
 </sst>
 </file>
@@ -170,7 +170,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -218,9 +218,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -253,10 +254,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Followed Hyperlink" xfId="1" builtinId="9" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -28570,6 +28572,9 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C9" r:id="rId1" xr:uid="{304D9982-8DFF-9446-B2FF-0E75B1C7C4BA}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <extLst>
